--- a/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_Maternity_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_Maternity_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssivasubram9\ORBIS PAS UKI-LZO (1)\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\IP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\IP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447F983C-4B73-42A8-A0CA-0B5FA687E9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DE8A56-B757-4AFB-9EE6-9FD023B90532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D3500964-6628-424E-8BE7-11D673AE8DC7}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{D3500964-6628-424E-8BE7-11D673AE8DC7}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -2250,7 +2250,7 @@
         <v>222</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
